--- a/nuevos ajustes balances.xlsx
+++ b/nuevos ajustes balances.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intaarg-my.sharepoint.com/personal/lewczuk_nuria_inta_gob_ar/Documents/Escritorio/shiny_app/app_EMCBalcarce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intaarg-my.sharepoint.com/personal/lewczuk_nuria_inta_gob_ar/Documents/shiny_app/app_EMCBalcarce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{459F905E-98A3-4694-BFDA-1EAB5535F742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B46F0BB-5F37-438A-97AB-BAFF81FF99CD}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{459F905E-98A3-4694-BFDA-1EAB5535F742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D31763E7-3D55-443E-81DC-45C5AD85DA08}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A3CD99E-36A0-4674-BF80-FF862D38565D}"/>
   </bookViews>
@@ -2503,6 +2503,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2510,7 +2511,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4064,6 +4064,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4071,7 +4072,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5673,6 +5673,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5680,7 +5681,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7234,6 +7234,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7241,7 +7242,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9479,6 +9479,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9486,7 +9487,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12496,10 +12496,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -12823,10 +12819,13 @@
     <col min="1" max="1" width="13.7109375" style="7" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="7" customWidth="1"/>
     <col min="3" max="3" width="7.7109375" style="4" customWidth="1"/>
-    <col min="4" max="6" width="4.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" style="4" customWidth="1"/>
-    <col min="9" max="15" width="6.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10" style="4" customWidth="1"/>
+    <col min="10" max="15" width="6.28515625" style="4" customWidth="1"/>
     <col min="16" max="16" width="6.28515625" style="7" customWidth="1"/>
     <col min="17" max="21" width="6.28515625" style="4" customWidth="1"/>
     <col min="22" max="31" width="6.28515625" style="4" hidden="1" customWidth="1"/>
